--- a/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/exportDiscloseRecord12.xlsx
+++ b/Ft-Cloud/ft-services/ft-service-pm/src/main/resources/template/exportDiscloseRecord12.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jinhaochen\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\kf-project\hhwy_szjt\opmp\Ft-Cloud\ft-services\ft-service-pm\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36ECD4E6-3A8D-42B2-BE53-ABFB0D71AD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9B09228-0305-447A-99F3-C256C225E58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,12 +132,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -464,7 +470,7 @@
     <col min="6" max="6" width="16.77734375" customWidth="1"/>
     <col min="7" max="7" width="12.109375" customWidth="1"/>
     <col min="8" max="8" width="12.109375" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
+    <col min="9" max="9" width="14.33203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="13.77734375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -493,7 +499,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
